--- a/assets/files/Mini-Dashboard.xlsx
+++ b/assets/files/Mini-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B700AF81-462C-40A6-8614-A8CF3D8CFFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C50C65-C664-4577-A705-230C9200275E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EAE9B6DC-016F-4F5B-9E7C-FC1FA5438351}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="12">
   <si>
     <t>Bulan</t>
   </si>
@@ -87,25 +87,13 @@
   <si>
     <t>Total</t>
   </si>
-  <si>
-    <t>Data Penjualan Multi-Dimensi</t>
-  </si>
-  <si>
-    <t>Tabel Rekap per Bulan</t>
-  </si>
-  <si>
-    <t>Tabel Rekap per Produk</t>
-  </si>
-  <si>
-    <t>Tabel Rekap per Region</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -152,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -267,24 +255,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -383,13 +353,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -397,79 +367,37 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -546,13 +474,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -565,6 +486,48 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -635,7 +598,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Referensi!$G$2</c:f>
+              <c:f>Referensi!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -670,7 +633,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Referensi!$F$3:$F$5</c:f>
+              <c:f>Referensi!$F$2:$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -687,7 +650,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Referensi!$G$3:$G$5</c:f>
+              <c:f>Referensi!$G$2:$G$4</c:f>
               <c:numCache>
                 <c:formatCode>_-"Rp"* #,##0_-;\-"Rp"* #,##0_-;_-"Rp"* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="3"/>
@@ -936,7 +899,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Referensi!$J$2</c:f>
+              <c:f>Referensi!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1040,7 +1003,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Referensi!$I$3:$I$4</c:f>
+              <c:f>Referensi!$I$2:$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -1054,7 +1017,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Referensi!$J$3:$J$4</c:f>
+              <c:f>Referensi!$J$2:$J$3</c:f>
               <c:numCache>
                 <c:formatCode>_-"Rp"* #,##0_-;\-"Rp"* #,##0_-;_-"Rp"* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1182,6 +1145,34 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Penjualan per Region</a:t>
+            </a:r>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1223,7 +1214,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Referensi!$M$2</c:f>
+              <c:f>Referensi!$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1244,7 +1235,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Referensi!$L$3:$L$4</c:f>
+              <c:f>Referensi!$L$2:$L$3</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -1258,7 +1249,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Referensi!$M$3:$M$4</c:f>
+              <c:f>Referensi!$M$2:$M$3</c:f>
               <c:numCache>
                 <c:formatCode>_-"Rp"* #,##0_-;\-"Rp"* #,##0_-;_-"Rp"* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3224,8 +3215,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Produk">
@@ -3248,7 +3239,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3302,8 +3293,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Region">
@@ -3326,7 +3317,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3398,13 +3389,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8A665D0-AEB6-4C9D-ACD0-5B9DDED4FF95}" name="Table1" displayName="Table1" ref="A2:D14" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
-  <autoFilter ref="A2:D14" xr:uid="{E8A665D0-AEB6-4C9D-ACD0-5B9DDED4FF95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8A665D0-AEB6-4C9D-ACD0-5B9DDED4FF95}" name="Table1" displayName="Table1" ref="A1:D13" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="A1:D13" xr:uid="{E8A665D0-AEB6-4C9D-ACD0-5B9DDED4FF95}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{611DCC1C-64EF-4F2C-8C11-AE38E6A6FD96}" name="Bulan" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{FC1E98BC-9F2B-4DCE-8464-3C9DAB2D097D}" name="Region" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{16A86CEB-7F34-47A4-81E1-F78DCBF2ECE0}" name="Produk" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{3F04351C-72BE-434C-A0BB-20B90F68A7E1}" name="Penjualan" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{611DCC1C-64EF-4F2C-8C11-AE38E6A6FD96}" name="Bulan" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{FC1E98BC-9F2B-4DCE-8464-3C9DAB2D097D}" name="Region" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{16A86CEB-7F34-47A4-81E1-F78DCBF2ECE0}" name="Produk" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{3F04351C-72BE-434C-A0BB-20B90F68A7E1}" name="Penjualan" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3729,76 +3720,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2F2D3B-F1A8-4A65-9014-852EEF49A4AC}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="7.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="7.42578125" style="12"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="15"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="M3" s="14"/>
+      <c r="D3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="M3" s="11"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="M4" s="14"/>
+      <c r="D4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="M4" s="11"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D6" s="14"/>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D7" s="14"/>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D8" s="14"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D9" s="14"/>
+      <c r="D9" s="11"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D10" s="14"/>
+      <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D11" s="14"/>
+      <c r="D11" s="11"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D12" s="14"/>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D13" s="14"/>
+      <c r="D13" s="11"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D14" s="14"/>
+      <c r="D14" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3816,7 +3804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8647499B-B196-45E1-B3E5-6BD4AFD6998D}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="1"/>
@@ -3827,282 +3815,268 @@
     <col min="13" max="13" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="F1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="I1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="11"/>
-      <c r="L1" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="11"/>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>11</v>
+      <c r="A2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="14">
+        <v>50000000</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3">
+        <f>SUMIF(A2:$A$13,F2,$D$2:$D$13)</f>
+        <v>208000000</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="7">
+        <f>SUMIF($C$2:$C$13,I2,$D$2:$D$13)</f>
+        <v>247000000</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="7">
+        <f>SUMIF($B$2:$B$13,L2,$D$2:$D$13)</f>
+        <v>255000000</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="14">
+        <v>30000000</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3">
+        <f>SUMIF(A3:$A$13,F3,$D$2:$D$13)</f>
+        <v>55000000</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="9">
+        <f>SUMIF($C$2:$C$13,I3,$D$2:$D$13)</f>
+        <v>157000000</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="9">
+        <f>SUMIF($B$2:$B$13,L3,$D$2:$D$13)</f>
+        <v>149000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="17">
-        <v>50000000</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="3">
-        <f>SUMIF(A3:$A$14,F3,$D$3:$D$14)</f>
-        <v>208000000</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="7">
-        <f>SUMIF($C$3:$C$14,I3,$D$3:$D$14)</f>
-        <v>247000000</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="7">
-        <f>SUMIF($B$3:$B$14,L3,$D$3:$D$14)</f>
-        <v>255000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="17">
-        <v>30000000</v>
+      <c r="D4" s="14">
+        <v>25000000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="3">
-        <f>SUMIF(A4:$A$14,F4,$D$3:$D$14)</f>
-        <v>55000000</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="9">
-        <f>SUMIF($C$3:$C$14,I4,$D$3:$D$14)</f>
-        <v>157000000</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="9">
-        <f>SUMIF($B$3:$B$14,L4,$D$3:$D$14)</f>
-        <v>149000000</v>
+        <f>SUMIF(A4:$A$13,F4,$D$2:$D$13)</f>
+        <v>141000000</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="17">
-        <v>25000000</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3">
-        <f>SUMIF(A5:$A$14,F5,$D$3:$D$14)</f>
-        <v>141000000</v>
+        <v>7</v>
+      </c>
+      <c r="D5" s="14">
+        <v>20000000</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="17">
-        <v>20000000</v>
+        <v>6</v>
+      </c>
+      <c r="D6" s="14">
+        <v>55000000</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="17">
-        <v>55000000</v>
+        <v>7</v>
+      </c>
+      <c r="D7" s="14">
+        <v>28000000</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>4</v>
+      <c r="A8" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="17">
-        <v>28000000</v>
+        <v>6</v>
+      </c>
+      <c r="D8" s="14">
+        <v>27000000</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="17">
-        <v>27000000</v>
+        <v>7</v>
+      </c>
+      <c r="D9" s="14">
+        <v>22000000</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>9</v>
+      <c r="A10" s="13" t="s">
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="17">
-        <v>22000000</v>
+        <v>6</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60000000</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="17">
-        <v>60000000</v>
+        <v>7</v>
+      </c>
+      <c r="D11" s="14">
+        <v>32000000</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="17">
-        <v>32000000</v>
+        <v>6</v>
+      </c>
+      <c r="D12" s="14">
+        <v>30000000</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="17">
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="22" t="s">
+      <c r="C13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D13" s="20">
         <v>25000000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="L1:M1"/>
-  </mergeCells>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
